--- a/weeks/◆ 2026년 09월 2주 편성표 (0907 ~ 0913).xlsx
+++ b/weeks/◆ 2026년 09월 2주 편성표 (0907 ~ 0913).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -236,14 +236,8 @@
       <color rgb="00333333"/>
       <u val="none"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,11 +282,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDFFC6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -360,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -468,7 +457,7 @@
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
+      <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
@@ -476,13 +465,10 @@
     <xf numFmtId="49" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="34" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="35" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -499,48 +485,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -587,7 +573,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -904,17 +890,17 @@
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="L8" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M8" s="32" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'패션2Lab'</t>
+        </is>
+      </c>
+      <c r="M8" s="31" t="inlineStr">
+        <is>
+          <t>에이앤디 니트 재킷</t>
         </is>
       </c>
       <c r="N8" s="25"/>
@@ -930,17 +916,17 @@
       </c>
       <c r="Q8" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="R8" s="31" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
-        </is>
-      </c>
-      <c r="S8" s="31" t="inlineStr">
-        <is>
-          <t>에이앤디 니트 재킷</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="S8" s="32" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="T8" s="25"/>
@@ -954,36 +940,36 @@
           <t>55</t>
         </is>
       </c>
-      <c r="W8" s="30" t="inlineStr">
+      <c r="W8" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="Y8" s="31" t="inlineStr">
+        <is>
+          <t>스케쳐스 밥스 하이 슬립인스</t>
+        </is>
+      </c>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="29" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="AB8" s="24" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AC8" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
-        </is>
-      </c>
-      <c r="X8" s="31" t="inlineStr">
-        <is>
-          <t>'건강식품2'</t>
-        </is>
-      </c>
-      <c r="Y8" s="31" t="inlineStr">
-        <is>
-          <t>오리진 야생베리</t>
-        </is>
-      </c>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="29" t="inlineStr">
-        <is>
-          <t>05:20</t>
-        </is>
-      </c>
-      <c r="AB8" s="24" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AC8" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
         </is>
       </c>
       <c r="AD8" s="31" t="inlineStr">
@@ -1066,125 +1052,125 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
+        </is>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
-        <is>
-          <t>'패션4Lab'</t>
-        </is>
-      </c>
-      <c r="G9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비버리힐즈폴로클럽 26FW 케이블 가디건 </t>
-        </is>
-      </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>가히 캐비어밤</t>
+        </is>
+      </c>
+      <c r="N9" s="25"/>
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t>06:15</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="R9" s="31" t="inlineStr">
+        <is>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="inlineStr">
+        <is>
+          <t>비에날씬 프로</t>
+        </is>
+      </c>
+      <c r="T9" s="25"/>
+      <c r="U9" s="29" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="V9" s="33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="W9" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="X9" s="31" t="inlineStr">
+        <is>
+          <t>'패션2Lab'</t>
+        </is>
+      </c>
+      <c r="Y9" s="34" t="inlineStr">
+        <is>
+          <t>에이앤디 간절기 상품 클리어런스</t>
+        </is>
+      </c>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="29" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AB9" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC9" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="M9" s="31" t="inlineStr">
-        <is>
-          <t>가히 캐비어밤</t>
-        </is>
-      </c>
-      <c r="N9" s="25"/>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="P9" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q9" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="R9" s="31" t="inlineStr">
-        <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="S9" s="31" t="inlineStr">
-        <is>
-          <t>비에날씬 프로</t>
-        </is>
-      </c>
-      <c r="T9" s="25"/>
-      <c r="U9" s="29" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="V9" s="33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="W9" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="X9" s="31" t="inlineStr">
-        <is>
-          <t>'패션2Lab'</t>
-        </is>
-      </c>
-      <c r="Y9" s="34" t="inlineStr">
-        <is>
-          <t>에이앤디 간절기 상품 클리어런스</t>
-        </is>
-      </c>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="29" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="AB9" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AC9" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
       <c r="AD9" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="AE9" s="32" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'패션4Lab'</t>
+        </is>
+      </c>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비버리힐즈폴로클럽 26FW 케이블 가디건 </t>
         </is>
       </c>
       <c r="AF9" s="25"/>
@@ -1341,7 +1327,7 @@
       </c>
       <c r="W10" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>중</t>
         </is>
       </c>
       <c r="X10" s="31" t="inlineStr">
@@ -1351,7 +1337,7 @@
       </c>
       <c r="Y10" s="34" t="inlineStr">
         <is>
-          <t>스케쳐스 맥스쿠셔닝 아우라</t>
+          <t>슈올즈 카이로스 라이드</t>
         </is>
       </c>
       <c r="Z10" s="25"/>
@@ -1531,20 +1517,19 @@
           <t>70</t>
         </is>
       </c>
-      <c r="W11" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="W11" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="X11" s="31" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
+          <t>'레포츠'</t>
         </is>
       </c>
       <c r="Y11" s="31" t="inlineStr">
         <is>
-          <t>리터니티 율무팩</t>
+          <t>에스카다 26FW</t>
         </is>
       </c>
       <c r="Z11" s="25"/>
@@ -1671,19 +1656,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="L12" s="31" t="inlineStr">
         <is>
-          <t>'레포츠'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="M12" s="31" t="inlineStr">
         <is>
-          <t>에스카다 26FW</t>
+          <t>셀폰즈 녹는실앰플</t>
         </is>
       </c>
       <c r="N12" s="25"/>
@@ -1998,12 +1984,12 @@
       </c>
       <c r="AP13" s="31" t="inlineStr">
         <is>
-          <t>'뷰티브랜드'</t>
+          <t>'뷰티1'</t>
         </is>
       </c>
       <c r="AQ13" s="31" t="inlineStr">
         <is>
-          <t>글램팜 고데기 GP201</t>
+          <t>리터니티 율무팩</t>
         </is>
       </c>
     </row>
@@ -2243,20 +2229,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="L15" s="31" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>'일반식품1'</t>
         </is>
       </c>
       <c r="M15" s="31" t="inlineStr">
         <is>
-          <t>라포레 플레이팅팬</t>
+          <t>[명절]두리담 송편</t>
         </is>
       </c>
       <c r="N15" s="25"/>
@@ -2277,12 +2262,12 @@
       </c>
       <c r="R15" s="31" t="inlineStr">
         <is>
-          <t>'GA'</t>
-        </is>
-      </c>
-      <c r="S15" s="37" t="inlineStr">
-        <is>
-          <t>#금융GA</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="S15" s="32" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="T15" s="25"/>
@@ -2303,12 +2288,12 @@
       </c>
       <c r="X15" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
+          <t>'GA'</t>
         </is>
       </c>
       <c r="Y15" s="37" t="inlineStr">
         <is>
-          <t>#금융상품</t>
+          <t>#금융GA</t>
         </is>
       </c>
       <c r="Z15" s="25"/>
@@ -2332,7 +2317,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AE15" s="32" t="inlineStr">
+      <c r="AE15" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2434,19 +2419,20 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="K16" s="30" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="L16" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M16" s="32" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="M16" s="31" t="inlineStr">
+        <is>
+          <t>삼성 냉장고</t>
         </is>
       </c>
       <c r="N16" s="25"/>
@@ -2561,7 +2547,7 @@
           <t>14:55</t>
         </is>
       </c>
-      <c r="AN16" s="35" t="inlineStr">
+      <c r="AN16" s="24" t="inlineStr">
         <is>
           <t>75</t>
         </is>
@@ -2577,7 +2563,7 @@
           <t>'주방'</t>
         </is>
       </c>
-      <c r="AQ16" s="36" t="inlineStr">
+      <c r="AQ16" s="31" t="inlineStr">
         <is>
           <t>칼만 최고급 통5중 저압냄비</t>
         </is>
@@ -2627,20 +2613,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K17" s="30" t="inlineStr">
-        <is>
-          <t>수
-수</t>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
         </is>
       </c>
       <c r="L17" s="31" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>'뷰티1'</t>
         </is>
       </c>
       <c r="M17" s="31" t="inlineStr">
         <is>
-          <t>테팔 그릴</t>
+          <t>히말라야 수분크림</t>
         </is>
       </c>
       <c r="N17" s="25"/>
@@ -2664,7 +2649,7 @@
           <t>'일반렌탈'</t>
         </is>
       </c>
-      <c r="S17" s="37" t="inlineStr">
+      <c r="S17" s="32" t="inlineStr">
         <is>
           <t>더케이예다함 상조</t>
         </is>
@@ -2736,18 +2721,18 @@
       </c>
       <c r="AI17" s="30" t="inlineStr">
         <is>
-          <t>수
+          <t>중
 수</t>
         </is>
       </c>
       <c r="AJ17" s="31" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'주얼리'</t>
         </is>
       </c>
       <c r="AK17" s="31" t="inlineStr">
         <is>
-          <t>팀P-그란츠 치약</t>
+          <t>골드라벨 24K</t>
         </is>
       </c>
       <c r="AL17" s="25"/>
@@ -2756,7 +2741,7 @@
           <t>16:10</t>
         </is>
       </c>
-      <c r="AN17" s="35" t="inlineStr">
+      <c r="AN17" s="24" t="inlineStr">
         <is>
           <t>65</t>
         </is>
@@ -2771,7 +2756,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="AQ17" s="36" t="inlineStr">
+      <c r="AQ17" s="31" t="inlineStr">
         <is>
           <t>[명절]워커힐 LA갈비</t>
         </is>
@@ -2818,23 +2803,23 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>대
+          <t>중
 수</t>
         </is>
       </c>
       <c r="L18" s="31" t="inlineStr">
         <is>
-          <t>'가전'</t>
+          <t>'주방'</t>
         </is>
       </c>
       <c r="M18" s="31" t="inlineStr">
         <is>
-          <t>LG 건조기</t>
+          <t>라포레 플레이팅팬</t>
         </is>
       </c>
       <c r="N18" s="25"/>
@@ -2872,77 +2857,77 @@
       </c>
       <c r="V18" s="35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="W18" s="30" t="inlineStr">
+        <is>
+          <t>수
+수</t>
+        </is>
+      </c>
+      <c r="X18" s="31" t="inlineStr">
+        <is>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="Y18" s="39" t="inlineStr">
+        <is>
+          <t>비에날씬 프로</t>
+        </is>
+      </c>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="29" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AB18" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC18" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="X18" s="31" t="inlineStr">
-        <is>
-          <t>'일반식품1'</t>
-        </is>
-      </c>
-      <c r="Y18" s="36" t="inlineStr">
-        <is>
-          <t>거창북부 홍로</t>
-        </is>
-      </c>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="29" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AB18" s="24" t="inlineStr">
+      <c r="AD18" s="31" t="inlineStr">
+        <is>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>헤르젠 쌀냉장고</t>
+        </is>
+      </c>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="29" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AC18" s="30" t="inlineStr">
+      <c r="AI18" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="AD18" s="31" t="inlineStr">
-        <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>헤르젠 쌀냉장고</t>
-        </is>
-      </c>
-      <c r="AF18" s="25"/>
-      <c r="AG18" s="29" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AI18" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
       <c r="AJ18" s="31" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>'뷰티브랜드'</t>
         </is>
       </c>
       <c r="AK18" s="31" t="inlineStr">
         <is>
-          <t>리브이셀 레티 콜라겐 랩핑 마스크</t>
+          <t>헤베스템 랩핑 마스크</t>
         </is>
       </c>
       <c r="AL18" s="25"/>
@@ -2992,23 +2977,23 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="F19" s="31" t="inlineStr">
         <is>
-          <t>'액티브라이프'</t>
-        </is>
-      </c>
-      <c r="G19" s="31" t="inlineStr">
-        <is>
-          <t>[전국한우협회] 한우 1++ 넘버나인 구이</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="H19" s="25"/>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="J19" s="35" t="inlineStr">
@@ -3026,7 +3011,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="M19" s="36" t="inlineStr">
+      <c r="M19" s="39" t="inlineStr">
         <is>
           <t>숲에서자란 화고버섯 세트</t>
         </is>
@@ -3053,7 +3038,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="S19" s="36" t="inlineStr">
+      <c r="S19" s="39" t="inlineStr">
         <is>
           <t>위바이옴 두뇌엔닥터PS맥스(7~8불가)</t>
         </is>
@@ -3061,7 +3046,7 @@
       <c r="T19" s="25"/>
       <c r="U19" s="29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="V19" s="35" t="inlineStr">
@@ -3070,45 +3055,46 @@
         </is>
       </c>
       <c r="W19" s="30" t="inlineStr">
+        <is>
+          <t>중
+수</t>
+        </is>
+      </c>
+      <c r="X19" s="31" t="inlineStr">
+        <is>
+          <t>'일반식품1'</t>
+        </is>
+      </c>
+      <c r="Y19" s="39" t="inlineStr">
+        <is>
+          <t>거창북부 홍로</t>
+        </is>
+      </c>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="29" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AB19" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC19" s="30" t="inlineStr">
         <is>
           <t>수
 수</t>
         </is>
       </c>
-      <c r="X19" s="31" t="inlineStr">
-        <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="Y19" s="36" t="inlineStr">
-        <is>
-          <t>비에날씬 프로</t>
-        </is>
-      </c>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="29" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AB19" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AC19" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
       <c r="AD19" s="31" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
+          <t>'주방'</t>
         </is>
       </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>디아루체 26FW론칭</t>
+          <t>테팔 그릴</t>
         </is>
       </c>
       <c r="AF19" s="25"/>
@@ -3159,7 +3145,7 @@
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AQ19" s="39" t="inlineStr">
+      <c r="AQ19" s="40" t="inlineStr">
         <is>
           <t>교원투어 서유럽</t>
         </is>
@@ -3192,7 +3178,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G20" s="39" t="inlineStr">
+      <c r="G20" s="40" t="inlineStr">
         <is>
           <t>농협 상주곶감</t>
         </is>
@@ -3200,28 +3186,27 @@
       <c r="H20" s="25"/>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J20" s="35" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K20" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="L20" s="31" t="inlineStr">
         <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="M20" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">칼만 통3중 저압냄비 </t>
+          <t>'액티브라이프'</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr">
+        <is>
+          <t>[전국한우협회] 한우 1++ 넘버나인 구이</t>
         </is>
       </c>
       <c r="N20" s="25"/>
@@ -3246,7 +3231,7 @@
           <t>'건강식품1'</t>
         </is>
       </c>
-      <c r="S20" s="36" t="inlineStr">
+      <c r="S20" s="39" t="inlineStr">
         <is>
           <t>덴마크 유산균이야기</t>
         </is>
@@ -3254,12 +3239,12 @@
       <c r="T20" s="25"/>
       <c r="U20" s="29" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="V20" s="35" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W20" s="24" t="inlineStr">
@@ -3272,7 +3257,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="Y20" s="36" t="inlineStr">
+      <c r="Y20" s="39" t="inlineStr">
         <is>
           <t>보넬드 당근주스</t>
         </is>
@@ -3384,7 +3369,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G21" s="39" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>철원 오대쌀</t>
         </is>
@@ -3462,7 +3447,7 @@
           <t>'건강식품2'</t>
         </is>
       </c>
-      <c r="Y21" s="36" t="inlineStr">
+      <c r="Y21" s="39" t="inlineStr">
         <is>
           <t>주영 콘드로이친</t>
         </is>
@@ -3576,7 +3561,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G22" s="37" t="inlineStr">
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3599,12 +3584,12 @@
       </c>
       <c r="L22" s="31" t="inlineStr">
         <is>
-          <t>'GA'</t>
-        </is>
-      </c>
-      <c r="M22" s="32" t="inlineStr">
-        <is>
-          <t>#금융GA</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M22" s="37" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="N22" s="25"/>
@@ -3681,7 +3666,7 @@
           <t>'주방'</t>
         </is>
       </c>
-      <c r="AE22" s="36" t="inlineStr">
+      <c r="AE22" s="39" t="inlineStr">
         <is>
           <t>조이락 트라이탄 밀폐용기</t>
         </is>
@@ -3725,7 +3710,7 @@
       </c>
       <c r="AO22" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AP22" s="31" t="inlineStr">
@@ -3735,7 +3720,7 @@
       </c>
       <c r="AQ22" s="31" t="inlineStr">
         <is>
-          <t>[명절]제주 마농포갈비 (3.6kg 139)</t>
+          <t>[명절]신세계 호주산 원육</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3751,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G23" s="39" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>수산대전-제주가마당 은갈치</t>
         </is>
@@ -3846,7 +3831,7 @@
       </c>
       <c r="Y23" s="31" t="inlineStr">
         <is>
-          <t>팀P-[명절]청기와타운 포갈비 (2.1kg 149)</t>
+          <t>[명절]제주 마농포갈비 (3.6kg 139)</t>
         </is>
       </c>
       <c r="Z23" s="25"/>
@@ -3870,7 +3855,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="AE23" s="36" t="inlineStr">
+      <c r="AE23" s="39" t="inlineStr">
         <is>
           <t>[명절]박정수 벽돌갈비</t>
         </is>
@@ -3913,20 +3898,19 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO23" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="AP23" s="31" t="inlineStr">
         <is>
-          <t>'국내여행'</t>
-        </is>
-      </c>
-      <c r="AQ23" s="31" t="inlineStr">
-        <is>
-          <t>휘닉스 평창</t>
+          <t>'GA'</t>
+        </is>
+      </c>
+      <c r="AQ23" s="37" t="inlineStr">
+        <is>
+          <t>#금융GA</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3941,7 @@
           <t>'일반식품2'</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t>마스터 블렌드 7</t>
         </is>
@@ -4108,17 +4092,17 @@
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AP24" s="31" t="inlineStr">
         <is>
-          <t>'GA'</t>
-        </is>
-      </c>
-      <c r="AQ24" s="37" t="inlineStr">
-        <is>
-          <t>#금융GA</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="AQ24" s="31" t="inlineStr">
+        <is>
+          <t>한국중앙금거래소 24K</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4133,7 @@
           <t>'주방'</t>
         </is>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>알텐바흐 프라이팬</t>
         </is>
@@ -4175,13 +4159,13 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M25" s="32" t="inlineStr">
+      <c r="M25" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="N25" s="25"/>
-      <c r="O25" s="40" t="inlineStr">
+      <c r="O25" s="29" t="inlineStr">
         <is>
           <t>21:10</t>
         </is>
@@ -4193,17 +4177,17 @@
       </c>
       <c r="Q25" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="R25" s="31" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S25" s="41" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="S25" s="34" t="inlineStr">
+        <is>
+          <t>디원밀라노 시계</t>
         </is>
       </c>
       <c r="T25" s="25"/>
@@ -4331,18 +4315,18 @@
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>중
+          <t>수
 수</t>
         </is>
       </c>
       <c r="F26" s="31" t="inlineStr">
         <is>
-          <t>'잡화'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="G26" s="31" t="inlineStr">
         <is>
-          <t>베라왕 T스트랩 로퍼</t>
+          <t>캐롤프랑크 클렌저</t>
         </is>
       </c>
       <c r="H26" s="25"/>
@@ -4409,19 +4393,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W26" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W26" s="30" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="X26" s="31" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
+          <t>'가전'</t>
         </is>
       </c>
       <c r="Y26" s="31" t="inlineStr">
         <is>
-          <t>V1969트위드 니트재킷 外</t>
+          <t>로보락F25 ACE</t>
         </is>
       </c>
       <c r="Z26" s="25"/>
@@ -4515,7 +4500,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G27" s="37" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -4531,20 +4516,19 @@
           <t>65</t>
         </is>
       </c>
-      <c r="K27" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="L27" s="31" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="M27" s="31" t="inlineStr">
-        <is>
-          <t>토리든 앰플</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M27" s="37" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="N27" s="25"/>
@@ -4732,19 +4716,20 @@
           <t>65</t>
         </is>
       </c>
-      <c r="Q28" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="Q28" s="30" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="R28" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="S28" s="37" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="S28" s="31" t="inlineStr">
+        <is>
+          <t>이지듀 기미앰플</t>
         </is>
       </c>
       <c r="T28" s="25"/>
